--- a/results/Int All Data 0.3/Linea_fi_all.xlsx
+++ b/results/Int All Data 0.3/Linea_fi_all.xlsx
@@ -1566,7 +1566,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.007886309047237838 +/- 0.0014768508203119766</t>
+          <t>-0.007926341072858334 +/- 0.0014741355195774094</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.00012009607686148671 +/- 0.00025633003352412795</t>
+          <t>0.0001601281024819823 +/- 0.00026554241716215623</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.00021017234131986973 +/- 0.004539917172358335</t>
+          <t>0.00012610340479191073 +/- 0.004523541601887438</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>0.0068095838587641675 +/- 0.0023911664822745564</t>
+          <t>0.006767549390500194 +/- 0.002439810317096505</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.0013836477987421492 +/- 0.001044858347536863</t>
+          <t>-0.0014255765199161496 +/- 0.0010804275661823962</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.00033542976939202605 +/- 0.0006162238346624437</t>
+          <t>0.00037735849056602655 +/- 0.0006876821579394867</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.01292157659488009 +/- 0.0014169521149258726</t>
+          <t>0.012962210483543235 +/- 0.0014701383596201299</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.015603413246647668 +/- 0.002603107253644345</t>
+          <t>0.015562779357984525 +/- 0.002621122051665177</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.0010403662089054743 +/- 0.001962959037048822</t>
+          <t>0.0009987515605492602 +/- 0.001980087765854406</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>0.04544319600499371 +/- 0.003544825541247924</t>
+          <t>0.04540158135663749 +/- 0.0034740131774349333</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.008434746118338188 +/- 0.002362311027282841</t>
+          <t>0.008392782207301686 +/- 0.0023886276912727894</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.001594628619387284 +/- 0.0018653890701546578</t>
+          <t>0.0016365925304237861 +/- 0.0018995334112893304</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>0.03281577843054969 +/- 0.0025649528812314126</t>
+          <t>0.03285774234158619 +/- 0.002546002738080998</t>
         </is>
       </c>
       <c r="DL7" t="inlineStr">
@@ -5666,74 +5666,74 @@
       </c>
       <c r="DO7" t="inlineStr">
         <is>
+          <t>0.051154007553503945 +/- 0.004552455812322634</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>0.02249265631556856 +/- 0.005775795395412594</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>-0.0003357112882921176 +/- 0.0005241290808559367</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>-0.0003357112882921176 +/- 0.0005241290808559367</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>0.0005035669324380598 +/- 0.0005874947545111133</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>0.18405371380612667 +/- 0.00502937079868355</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>0.08917331095258073 +/- 0.0042225370955724225</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>0.005119597146453991 +/- 0.0013636656994772916</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>0.005455308434746076 +/- 0.0015013465228701942</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>0.000503566932438071 +/- 0.0004111606786039821</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>0.019009651699538343 +/- 0.0022367197601739696</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>-0.0011330255979857817 +/- 0.0007973143096936589</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>-0.020226605119597185 +/- 0.0017179596718807295</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
           <t>0.05111204364246743 +/- 0.004553809472513808</t>
         </is>
       </c>
-      <c r="DP7" t="inlineStr">
-        <is>
-          <t>0.02249265631556856 +/- 0.005775795395412594</t>
-        </is>
-      </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>-0.0003357112882921176 +/- 0.0005241290808559367</t>
-        </is>
-      </c>
-      <c r="DR7" t="inlineStr">
-        <is>
-          <t>-0.0003357112882921176 +/- 0.0005241290808559367</t>
-        </is>
-      </c>
-      <c r="DS7" t="inlineStr">
-        <is>
-          <t>0.0005035669324380598 +/- 0.0005874947545111133</t>
-        </is>
-      </c>
-      <c r="DT7" t="inlineStr">
-        <is>
-          <t>0.18405371380612667 +/- 0.00502937079868355</t>
-        </is>
-      </c>
-      <c r="DU7" t="inlineStr">
-        <is>
-          <t>0.08917331095258073 +/- 0.0042225370955724225</t>
-        </is>
-      </c>
-      <c r="DV7" t="inlineStr">
-        <is>
-          <t>0.005119597146453991 +/- 0.0013636656994772916</t>
-        </is>
-      </c>
-      <c r="DW7" t="inlineStr">
-        <is>
-          <t>0.005455308434746076 +/- 0.0015013465228701942</t>
-        </is>
-      </c>
-      <c r="DX7" t="inlineStr">
-        <is>
-          <t>0.000503566932438071 +/- 0.0004111606786039821</t>
-        </is>
-      </c>
-      <c r="DY7" t="inlineStr">
-        <is>
-          <t>0.019009651699538343 +/- 0.0022367197601739696</t>
-        </is>
-      </c>
-      <c r="DZ7" t="inlineStr">
-        <is>
-          <t>-0.0011330255979857817 +/- 0.0007973143096936589</t>
-        </is>
-      </c>
-      <c r="EA7" t="inlineStr">
-        <is>
-          <t>-0.020226605119597185 +/- 0.0017179596718807295</t>
-        </is>
-      </c>
-      <c r="EB7" t="inlineStr">
-        <is>
-          <t>0.051154007553503945 +/- 0.004552455812322634</t>
-        </is>
-      </c>
       <c r="EC7" t="inlineStr">
         <is>
           <t>0.006966009232060366 +/- 0.0017423868646266735</t>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>0.02647922786403688 +/- 0.002399293723696652</t>
+          <t>0.02643726395300038 +/- 0.002425209110667203</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.007209106239460384 +/- 0.0013783965197530926</t>
+          <t>-0.0072512647554806246 +/- 0.00134379236513567</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.00012647554806068939 +/- 0.00032926853608374794</t>
+          <t>8.431703204044849e-05 +/- 0.000252951096121401</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="DX8" t="inlineStr">
         <is>
-          <t>-0.0002951096121416863 +/- 0.00019319459084976234</t>
+          <t>-0.0003372681281619272 +/- 0.0001686340640809636</t>
         </is>
       </c>
       <c r="DY8" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.0030456852791878155 +/- 0.0008153304575486606</t>
+          <t>-0.003006638032018738 +/- 0.0008563729870933786</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -8556,14 +8556,14 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
+          <t>0.0013947590870668103 +/- 0.0010361496764269944</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
           <t>0.0014370245139476267 +/- 0.0010557900250884945</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0.0013947590870668103 +/- 0.0010361496764269944</t>
-        </is>
-      </c>
       <c r="CA11" t="inlineStr">
         <is>
           <t>0.017455621301775182 +/- 0.0016155126672541416</t>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="ET11" t="inlineStr">
         <is>
-          <t>0.03279797125950975 +/- 0.0027792531230386446</t>
+          <t>0.03275570583262895 +/- 0.002779574479705388</t>
         </is>
       </c>
       <c r="EU11" t="inlineStr">
